--- a/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Phylum_by_Sample_Layer.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Layer/Archaea_Summary_Phylum_by_Sample_Layer.xlsx
@@ -581,10 +581,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>28.4481873777126</v>
+        <v>28.4546076167823</v>
       </c>
       <c r="D2" t="n">
-        <v>0.906443970678112</v>
+        <v>0.906870450926227</v>
       </c>
     </row>
     <row r="3">
@@ -595,10 +595,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5446721826474</v>
+        <v>17.5408160145974</v>
       </c>
       <c r="D3" t="n">
-        <v>1.72561176775621</v>
+        <v>1.72528647982215</v>
       </c>
     </row>
     <row r="4">
@@ -609,10 +609,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>17.4383623802787</v>
+        <v>17.4335608237773</v>
       </c>
       <c r="D4" t="n">
-        <v>0.57404082297464</v>
+        <v>0.573903827456795</v>
       </c>
     </row>
     <row r="5">
@@ -623,10 +623,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>9.5127443012037</v>
+        <v>9.51602264258472</v>
       </c>
       <c r="D5" t="n">
-        <v>0.580819329184073</v>
+        <v>0.581043017709981</v>
       </c>
     </row>
     <row r="6">
@@ -637,10 +637,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>9.32129889111748</v>
+        <v>9.32025122573027</v>
       </c>
       <c r="D6" t="n">
-        <v>2.18335948351444</v>
+        <v>2.18321937273215</v>
       </c>
     </row>
     <row r="7">
@@ -651,10 +651,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.89070541448611</v>
+        <v>8.89210505783201</v>
       </c>
       <c r="D7" t="n">
-        <v>1.69812350606266</v>
+        <v>1.69844039351303</v>
       </c>
     </row>
     <row r="8">
@@ -665,10 +665,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2.61567542300022</v>
+        <v>2.61572166037823</v>
       </c>
       <c r="D8" t="n">
-        <v>0.266309172716062</v>
+        <v>0.266328161330401</v>
       </c>
     </row>
     <row r="9">
@@ -679,10 +679,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>2.40931258302737</v>
+        <v>2.40857774457688</v>
       </c>
       <c r="D9" t="n">
-        <v>0.407562023169668</v>
+        <v>0.407427963649028</v>
       </c>
     </row>
     <row r="10">
@@ -693,10 +693,10 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>1.27604330034489</v>
+        <v>1.27570358577485</v>
       </c>
       <c r="D10" t="n">
-        <v>0.286174586870707</v>
+        <v>0.286113399427014</v>
       </c>
     </row>
     <row r="11">
@@ -707,10 +707,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>1.13570354228655</v>
+        <v>1.13533792434292</v>
       </c>
       <c r="D11" t="n">
-        <v>0.295003082334226</v>
+        <v>0.294899459749859</v>
       </c>
     </row>
     <row r="12">
@@ -721,10 +721,10 @@
         <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>0.842819608971247</v>
+        <v>0.843016143430554</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0557464320292799</v>
+        <v>0.0557795981523561</v>
       </c>
     </row>
     <row r="13">
@@ -735,10 +735,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>0.564474994923797</v>
+        <v>0.564279560192745</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0340832466395912</v>
+        <v>0.0340714462052048</v>
       </c>
     </row>
   </sheetData>
@@ -774,10 +774,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>23.6742255512446</v>
+        <v>23.6733054986631</v>
       </c>
       <c r="D2" t="n">
-        <v>1.17755476478765</v>
+        <v>1.17741229018617</v>
       </c>
     </row>
     <row r="3">
@@ -788,10 +788,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>21.165198269351</v>
+        <v>21.1661648954922</v>
       </c>
       <c r="D3" t="n">
-        <v>4.35471096040619</v>
+        <v>4.35471750744759</v>
       </c>
     </row>
     <row r="4">
@@ -802,10 +802,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>18.7585675464447</v>
+        <v>18.7596754229218</v>
       </c>
       <c r="D4" t="n">
-        <v>0.445227623743765</v>
+        <v>0.445256521377909</v>
       </c>
     </row>
     <row r="5">
@@ -816,10 +816,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>9.40355910464993</v>
+        <v>9.40208923435333</v>
       </c>
       <c r="D5" t="n">
-        <v>1.18539970027753</v>
+        <v>1.18527611735938</v>
       </c>
     </row>
     <row r="6">
@@ -830,10 +830,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.52226773244864</v>
+        <v>8.52260406917164</v>
       </c>
       <c r="D6" t="n">
-        <v>0.083296421579139</v>
+        <v>0.0833062168470663</v>
       </c>
     </row>
     <row r="7">
@@ -844,10 +844,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>5.50673856439945</v>
+        <v>5.50690544087976</v>
       </c>
       <c r="D7" t="n">
-        <v>0.776499732204651</v>
+        <v>0.776516936617608</v>
       </c>
     </row>
     <row r="8">
@@ -858,10 +858,10 @@
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>4.34393527695431</v>
+        <v>4.34320640356764</v>
       </c>
       <c r="D8" t="n">
-        <v>1.10234302665655</v>
+        <v>1.10215673471252</v>
       </c>
     </row>
     <row r="9">
@@ -872,10 +872,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>2.72315175441127</v>
+        <v>2.72301279020991</v>
       </c>
       <c r="D9" t="n">
-        <v>0.119683381183223</v>
+        <v>0.119670820428728</v>
       </c>
     </row>
     <row r="10">
@@ -886,10 +886,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>2.52308175706724</v>
+        <v>2.52339912345479</v>
       </c>
       <c r="D10" t="n">
-        <v>0.108456427509999</v>
+        <v>0.108471373000176</v>
       </c>
     </row>
     <row r="11">
@@ -900,10 +900,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>1.65170545677444</v>
+        <v>1.65209830648937</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0978593371195424</v>
+        <v>0.0978759074793054</v>
       </c>
     </row>
     <row r="12">
@@ -914,10 +914,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>1.58574655495638</v>
+        <v>1.5857200763407</v>
       </c>
       <c r="D12" t="n">
-        <v>0.149916665967348</v>
+        <v>0.149933979851808</v>
       </c>
     </row>
     <row r="13">
@@ -928,10 +928,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0980842454091233</v>
+        <v>0.0980799672171447</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0230756382404663</v>
+        <v>0.0230733844377137</v>
       </c>
     </row>
     <row r="14">
@@ -942,7 +942,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0437381858883574</v>
+        <v>0.0437387712383516</v>
       </c>
       <c r="D14"/>
     </row>
@@ -1172,10 +1172,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>26.1427513195863</v>
+        <v>26.1424498574997</v>
       </c>
       <c r="D2" t="n">
-        <v>1.19207859333435</v>
+        <v>1.19207377017358</v>
       </c>
     </row>
     <row r="3">
@@ -1186,10 +1186,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>24.6421608383319</v>
+        <v>24.6417854302772</v>
       </c>
       <c r="D3" t="n">
-        <v>4.50858756758852</v>
+        <v>4.50850291956916</v>
       </c>
     </row>
     <row r="4">
@@ -1200,10 +1200,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2655397706116</v>
+        <v>19.2658310749008</v>
       </c>
       <c r="D4" t="n">
-        <v>0.801037083083817</v>
+        <v>0.801053720061133</v>
       </c>
     </row>
     <row r="5">
@@ -1214,10 +1214,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>6.2228881538803</v>
+        <v>6.22275973219218</v>
       </c>
       <c r="D5" t="n">
-        <v>0.90493038320812</v>
+        <v>0.904867016254575</v>
       </c>
     </row>
     <row r="6">
@@ -1228,10 +1228,10 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>6.18294171350855</v>
+        <v>6.18296461430956</v>
       </c>
       <c r="D6" t="n">
-        <v>0.961367415170457</v>
+        <v>0.961392605156882</v>
       </c>
     </row>
     <row r="7">
@@ -1242,10 +1242,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>6.10970377577775</v>
+        <v>6.10983207065544</v>
       </c>
       <c r="D7" t="n">
-        <v>0.158972638112779</v>
+        <v>0.158974027986729</v>
       </c>
     </row>
     <row r="8">
@@ -1256,10 +1256,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>3.75698155890424</v>
+        <v>3.75746277574264</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0471719743357626</v>
+        <v>0.0471755139183538</v>
       </c>
     </row>
     <row r="9">
@@ -1270,10 +1270,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>3.69785524322662</v>
+        <v>3.69786767707835</v>
       </c>
       <c r="D9" t="n">
-        <v>0.239675529655952</v>
+        <v>0.239644160313435</v>
       </c>
     </row>
     <row r="10">
@@ -1284,10 +1284,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.90326694768316</v>
+        <v>2.90319495670332</v>
       </c>
       <c r="D10" t="n">
-        <v>0.174609789816148</v>
+        <v>0.174594607069973</v>
       </c>
     </row>
     <row r="11">
@@ -1298,10 +1298,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>0.583402176979545</v>
+        <v>0.583290982760341</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0870314764808729</v>
+        <v>0.0870157783826704</v>
       </c>
     </row>
     <row r="12">
@@ -1312,10 +1312,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>0.407956245260099</v>
+        <v>0.407987245009878</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04072813612845</v>
+        <v>0.0407363638337707</v>
       </c>
     </row>
     <row r="13">
@@ -1326,10 +1326,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>0.063016756916131</v>
+        <v>0.0630217691918993</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0106182411349641</v>
+        <v>0.0106206001393996</v>
       </c>
     </row>
     <row r="14">
@@ -1340,7 +1340,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0215354993342044</v>
+        <v>0.0215518136787733</v>
       </c>
       <c r="D14"/>
     </row>
@@ -1377,10 +1377,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>41.1226965728078</v>
+        <v>41.1181544407592</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1629152439783</v>
+        <v>1.16271391267712</v>
       </c>
     </row>
     <row r="3">
@@ -1391,10 +1391,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>17.8434585170669</v>
+        <v>17.8416914569284</v>
       </c>
       <c r="D3" t="n">
-        <v>4.07008793210061</v>
+        <v>4.06953710032304</v>
       </c>
     </row>
     <row r="4">
@@ -1405,10 +1405,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>14.0582988579708</v>
+        <v>14.0590133998972</v>
       </c>
       <c r="D4" t="n">
-        <v>3.93791648665836</v>
+        <v>3.93749478753898</v>
       </c>
     </row>
     <row r="5">
@@ -1419,10 +1419,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>12.5118933543116</v>
+        <v>12.5158221148857</v>
       </c>
       <c r="D5" t="n">
-        <v>4.84513813620268</v>
+        <v>4.84664378215444</v>
       </c>
     </row>
     <row r="6">
@@ -1433,10 +1433,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>6.13098740538092</v>
+        <v>6.13053053898012</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67413839306384</v>
+        <v>1.67401298260467</v>
       </c>
     </row>
     <row r="7">
@@ -1447,10 +1447,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5410657193669</v>
+        <v>4.54254025821407</v>
       </c>
       <c r="D7" t="n">
-        <v>1.26372211027965</v>
+        <v>1.26424553476954</v>
       </c>
     </row>
     <row r="8">
@@ -1461,10 +1461,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1.23810464156579</v>
+        <v>1.23831324980441</v>
       </c>
       <c r="D8" t="n">
-        <v>0.443668650252324</v>
+        <v>0.443766873470541</v>
       </c>
     </row>
     <row r="9">
@@ -1475,10 +1475,10 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.09845515103157</v>
+        <v>1.09861161623602</v>
       </c>
       <c r="D9" t="n">
-        <v>0.259735777881981</v>
+        <v>0.259767490523437</v>
       </c>
     </row>
     <row r="10">
@@ -1489,10 +1489,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0764610187463</v>
+        <v>1.07669850745551</v>
       </c>
       <c r="D10" t="n">
-        <v>0.186974950143159</v>
+        <v>0.18702418051521</v>
       </c>
     </row>
     <row r="11">
@@ -1503,10 +1503,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>0.272068552038335</v>
+        <v>0.272095187481516</v>
       </c>
       <c r="D11" t="n">
-        <v>0.112442581800846</v>
+        <v>0.112472967401727</v>
       </c>
     </row>
     <row r="12">
@@ -1517,7 +1517,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>0.106510209713172</v>
+        <v>0.106529229357992</v>
       </c>
       <c r="D12"/>
     </row>
@@ -1554,10 +1554,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>56.2950113123006</v>
+        <v>56.3041081219849</v>
       </c>
       <c r="D2" t="n">
-        <v>13.8490255669441</v>
+        <v>13.856182263946</v>
       </c>
     </row>
     <row r="3">
@@ -1568,10 +1568,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>19.0315436890672</v>
+        <v>19.0178896880278</v>
       </c>
       <c r="D3" t="n">
-        <v>3.434298153446</v>
+        <v>3.43025928737087</v>
       </c>
     </row>
     <row r="4">
@@ -1582,10 +1582,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>9.00862099460801</v>
+        <v>9.00828755411928</v>
       </c>
       <c r="D4" t="n">
-        <v>2.02215732061012</v>
+        <v>2.02190812977588</v>
       </c>
     </row>
     <row r="5">
@@ -1596,10 +1596,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>5.88310231003368</v>
+        <v>5.88431086826985</v>
       </c>
       <c r="D5" t="n">
-        <v>0.138331607450938</v>
+        <v>0.138386538948105</v>
       </c>
     </row>
     <row r="6">
@@ -1610,10 +1610,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>4.65985259507985</v>
+        <v>4.66228845333324</v>
       </c>
       <c r="D6" t="n">
-        <v>3.20270178727532</v>
+        <v>3.20458350215252</v>
       </c>
     </row>
     <row r="7">
@@ -1624,10 +1624,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>2.34896489837342</v>
+        <v>2.34939166093066</v>
       </c>
       <c r="D7" t="n">
-        <v>0.44256729333256</v>
+        <v>0.442612343283256</v>
       </c>
     </row>
     <row r="8">
@@ -1638,10 +1638,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.967041921835672</v>
+        <v>0.967424695406141</v>
       </c>
       <c r="D8" t="n">
-        <v>0.137633057761389</v>
+        <v>0.137743280417042</v>
       </c>
     </row>
     <row r="9">
@@ -1652,10 +1652,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>0.653944782403579</v>
+        <v>0.653790508001574</v>
       </c>
       <c r="D9" t="n">
-        <v>0.133944302900671</v>
+        <v>0.133970579529824</v>
       </c>
     </row>
     <row r="10">
@@ -1666,10 +1666,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.588808286603187</v>
+        <v>0.589228226734455</v>
       </c>
       <c r="D10" t="n">
-        <v>0.153594208763377</v>
+        <v>0.153807610433675</v>
       </c>
     </row>
     <row r="11">
@@ -1680,10 +1680,10 @@
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>0.294797111390009</v>
+        <v>0.294801554152728</v>
       </c>
       <c r="D11" t="n">
-        <v>0.060127286461208</v>
+        <v>0.0601038972054638</v>
       </c>
     </row>
     <row r="12">
@@ -1694,10 +1694,10 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>0.158091580006719</v>
+        <v>0.158217733902596</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0188193218025944</v>
+        <v>0.0188370960835982</v>
       </c>
     </row>
     <row r="13">
@@ -1708,10 +1708,10 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>0.110220518298119</v>
+        <v>0.110260935136766</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0450243073135336</v>
+        <v>0.0450239683206631</v>
       </c>
     </row>
   </sheetData>
@@ -1747,10 +1747,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>39.7402865718937</v>
+        <v>39.7412411980782</v>
       </c>
       <c r="D2" t="n">
-        <v>6.01956899505023</v>
+        <v>6.01933331621794</v>
       </c>
     </row>
     <row r="3">
@@ -1761,10 +1761,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>39.0856122201228</v>
+        <v>39.0836513901669</v>
       </c>
       <c r="D3" t="n">
-        <v>4.08107980810279</v>
+        <v>4.0808047933394</v>
       </c>
     </row>
     <row r="4">
@@ -1775,10 +1775,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>7.53251208659025</v>
+        <v>7.53238581525108</v>
       </c>
       <c r="D4" t="n">
-        <v>0.237454364070223</v>
+        <v>0.237447338734724</v>
       </c>
     </row>
     <row r="5">
@@ -1789,10 +1789,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>6.05739619676491</v>
+        <v>6.05777411828669</v>
       </c>
       <c r="D5" t="n">
-        <v>0.495695683395997</v>
+        <v>0.495746386644234</v>
       </c>
     </row>
     <row r="6">
@@ -1803,10 +1803,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>4.49248035946627</v>
+        <v>4.49296831660562</v>
       </c>
       <c r="D6" t="n">
-        <v>0.564843035012904</v>
+        <v>0.564871624703511</v>
       </c>
     </row>
     <row r="7">
@@ -1817,10 +1817,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>1.23303038835522</v>
+        <v>1.23305730173747</v>
       </c>
       <c r="D7" t="n">
-        <v>0.351368566230787</v>
+        <v>0.351388463161812</v>
       </c>
     </row>
     <row r="8">
@@ -1831,10 +1831,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>0.60323455124523</v>
+        <v>0.603305743940983</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0414114909026736</v>
+        <v>0.0414219625973653</v>
       </c>
     </row>
     <row r="9">
@@ -1845,10 +1845,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.558108885552207</v>
+        <v>0.558162676090998</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0461198226177086</v>
+        <v>0.0461237017220785</v>
       </c>
     </row>
     <row r="10">
@@ -1859,10 +1859,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.35006731271956</v>
+        <v>0.350143473310065</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0186100260221621</v>
+        <v>0.0186156707426802</v>
       </c>
     </row>
     <row r="11">
@@ -1873,10 +1873,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2535018465008</v>
+        <v>0.253525157028426</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0546702359334213</v>
+        <v>0.0546684509143556</v>
       </c>
     </row>
     <row r="12">
@@ -1887,10 +1887,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0500354950193752</v>
+        <v>0.0500356743516428</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0267642568796029</v>
+        <v>0.0267683469819272</v>
       </c>
     </row>
     <row r="13">
@@ -1901,10 +1901,10 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0437340857696056</v>
+        <v>0.0437491351519284</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0110594125551018</v>
+        <v>0.0110653480533512</v>
       </c>
     </row>
   </sheetData>
@@ -2081,10 +2081,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>91.3846293757945</v>
+        <v>91.3835487071044</v>
       </c>
       <c r="D2" t="n">
-        <v>0.858857861717626</v>
+        <v>0.859046215150375</v>
       </c>
     </row>
     <row r="3">
@@ -2095,10 +2095,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>4.29739103414817</v>
+        <v>4.2998423207784</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0933524972452613</v>
+        <v>0.0933985187150417</v>
       </c>
     </row>
     <row r="4">
@@ -2109,10 +2109,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>2.65365987314772</v>
+        <v>2.65422690068221</v>
       </c>
       <c r="D4" t="n">
-        <v>0.213133545685691</v>
+        <v>0.213293722340893</v>
       </c>
     </row>
     <row r="5">
@@ -2123,10 +2123,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>0.747320717623923</v>
+        <v>0.746077164710204</v>
       </c>
       <c r="D5" t="n">
-        <v>0.406402116738848</v>
+        <v>0.405727238535615</v>
       </c>
     </row>
     <row r="6">
@@ -2137,10 +2137,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>0.298005242007987</v>
+        <v>0.297697170490835</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0245469511332483</v>
+        <v>0.0245026224151622</v>
       </c>
     </row>
     <row r="7">
@@ -2151,10 +2151,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>0.242208681418132</v>
+        <v>0.242054191821643</v>
       </c>
       <c r="D7" t="n">
-        <v>0.120406148189222</v>
+        <v>0.120324411207035</v>
       </c>
     </row>
     <row r="8">
@@ -2165,10 +2165,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>0.233212573726985</v>
+        <v>0.23305415970703</v>
       </c>
       <c r="D8" t="n">
-        <v>0.111575935118184</v>
+        <v>0.111513697356389</v>
       </c>
     </row>
     <row r="9">
@@ -2179,7 +2179,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>0.081013606389594</v>
+        <v>0.0810849869124129</v>
       </c>
       <c r="D9"/>
     </row>
@@ -2191,10 +2191,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0625588957431237</v>
+        <v>0.0624143977927732</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00844884085840169</v>
+        <v>0.00842932580506875</v>
       </c>
     </row>
   </sheetData>
@@ -2230,10 +2230,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>57.749669817486</v>
+        <v>57.7496769827619</v>
       </c>
       <c r="D2" t="n">
-        <v>32.8647341787643</v>
+        <v>32.8647330880515</v>
       </c>
     </row>
     <row r="3">
@@ -2244,7 +2244,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>31.1608311737856</v>
+        <v>31.1608281680983</v>
       </c>
       <c r="D3"/>
     </row>
@@ -2256,7 +2256,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>8.10635960191601</v>
+        <v>8.10635394396169</v>
       </c>
       <c r="D4"/>
     </row>
@@ -2268,7 +2268,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>2.98313940681246</v>
+        <v>2.98314090517806</v>
       </c>
       <c r="D5"/>
     </row>
@@ -2305,10 +2305,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>94.0187702741291</v>
+        <v>94.0396963929599</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8363407254187</v>
+        <v>29.8417603709548</v>
       </c>
     </row>
     <row r="3">
@@ -2319,10 +2319,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>2.46890703144531</v>
+        <v>2.46278487288434</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08710525321409</v>
+        <v>0.0870575126095609</v>
       </c>
     </row>
     <row r="4">
@@ -2333,10 +2333,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>1.34512391076291</v>
+        <v>1.34075543492676</v>
       </c>
       <c r="D4" t="n">
-        <v>0.177064772229054</v>
+        <v>0.17636173727207</v>
       </c>
     </row>
     <row r="5">
@@ -2347,10 +2347,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>0.668717486193244</v>
+        <v>0.66478054693638</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0195973921296859</v>
+        <v>0.0194820266702645</v>
       </c>
     </row>
     <row r="6">
@@ -2361,10 +2361,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0.564676374514014</v>
+        <v>0.562772521004523</v>
       </c>
       <c r="D6" t="n">
-        <v>0.120104197176902</v>
+        <v>0.119891020436368</v>
       </c>
     </row>
     <row r="7">
@@ -2375,10 +2375,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.475114235888678</v>
+        <v>0.472317345520654</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0158246653491355</v>
+        <v>0.0157315269331347</v>
       </c>
     </row>
     <row r="8">
@@ -2389,10 +2389,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.190898338682771</v>
+        <v>0.190677332152804</v>
       </c>
       <c r="D8" t="n">
-        <v>0.064368226732903</v>
+        <v>0.0644377307378925</v>
       </c>
     </row>
     <row r="9">
@@ -2403,10 +2403,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>0.113316115693334</v>
+        <v>0.112649160697476</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00955278473866335</v>
+        <v>0.00949655946273129</v>
       </c>
     </row>
     <row r="10">
@@ -2417,10 +2417,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>0.105694253405797</v>
+        <v>0.105071841369835</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00655903092408336</v>
+        <v>0.00652037608813461</v>
       </c>
     </row>
     <row r="11">
@@ -2431,10 +2431,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0320131673348304</v>
+        <v>0.031824490762082</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00288790137493388</v>
+        <v>0.00287098879932759</v>
       </c>
     </row>
     <row r="12">
@@ -2445,7 +2445,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00965475140130624</v>
+        <v>0.00959795172690207</v>
       </c>
       <c r="D12"/>
     </row>
@@ -2457,7 +2457,7 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00711406054883688</v>
+        <v>0.00707210905824045</v>
       </c>
       <c r="D13"/>
     </row>
@@ -2494,10 +2494,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>30.1112711148218</v>
+        <v>30.1113600652968</v>
       </c>
       <c r="D2" t="n">
-        <v>1.52972477318495</v>
+        <v>1.52987360590041</v>
       </c>
     </row>
     <row r="3">
@@ -2508,10 +2508,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>18.1689234804074</v>
+        <v>18.1673264885753</v>
       </c>
       <c r="D3" t="n">
-        <v>0.432739320612276</v>
+        <v>0.432718841054423</v>
       </c>
     </row>
     <row r="4">
@@ -2522,10 +2522,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>18.0666572416679</v>
+        <v>18.0658656731335</v>
       </c>
       <c r="D4" t="n">
-        <v>3.12390449594885</v>
+        <v>3.12395351125932</v>
       </c>
     </row>
     <row r="5">
@@ -2536,10 +2536,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>9.01079721212342</v>
+        <v>9.01253857408425</v>
       </c>
       <c r="D5" t="n">
-        <v>0.103528975515545</v>
+        <v>0.103550337848236</v>
       </c>
     </row>
     <row r="6">
@@ -2550,10 +2550,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>8.94544697519405</v>
+        <v>8.94681254657371</v>
       </c>
       <c r="D6" t="n">
-        <v>1.43110346325025</v>
+        <v>1.43137024879891</v>
       </c>
     </row>
     <row r="7">
@@ -2564,10 +2564,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>4.17942439810022</v>
+        <v>4.17865556908465</v>
       </c>
       <c r="D7" t="n">
-        <v>0.629474802709262</v>
+        <v>0.629336454614041</v>
       </c>
     </row>
     <row r="8">
@@ -2578,10 +2578,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2.78975080444999</v>
+        <v>2.78941399814897</v>
       </c>
       <c r="D8" t="n">
-        <v>0.237114443555658</v>
+        <v>0.237065455423461</v>
       </c>
     </row>
     <row r="9">
@@ -2592,10 +2592,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>2.76752140081153</v>
+        <v>2.76760900747935</v>
       </c>
       <c r="D9" t="n">
-        <v>0.821765152469481</v>
+        <v>0.821789923031818</v>
       </c>
     </row>
     <row r="10">
@@ -2606,10 +2606,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>2.58416954572067</v>
+        <v>2.58453454734271</v>
       </c>
       <c r="D10" t="n">
-        <v>0.130127311213059</v>
+        <v>0.1301433272774</v>
       </c>
     </row>
     <row r="11">
@@ -2620,10 +2620,10 @@
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>1.54503415439421</v>
+        <v>1.54499986880777</v>
       </c>
       <c r="D11" t="n">
-        <v>0.250650727927502</v>
+        <v>0.250653674269885</v>
       </c>
     </row>
     <row r="12">
@@ -2634,10 +2634,10 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>1.49165246998783</v>
+        <v>1.4914708764406</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0731552420266889</v>
+        <v>0.0731462628143397</v>
       </c>
     </row>
     <row r="13">
@@ -2648,10 +2648,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>0.26521902396207</v>
+        <v>0.26530472662009</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0206940780505517</v>
+        <v>0.0206946981035593</v>
       </c>
     </row>
     <row r="14">
@@ -2662,7 +2662,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0741321783585579</v>
+        <v>0.0741080584124175</v>
       </c>
       <c r="D14"/>
     </row>
